--- a/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA67829-321F-46C8-9A12-BF64EFEEEBC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FE766B-09F4-4813-9926-9F604D654B89}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="额度信息" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
   <si>
     <t>区域</t>
   </si>
@@ -198,6 +198,24 @@
   </si>
   <si>
     <t>配件号/工具号</t>
+  </si>
+  <si>
+    <t>工单号</t>
+  </si>
+  <si>
+    <t>合同号</t>
+  </si>
+  <si>
+    <t>Sys ID</t>
+  </si>
+  <si>
+    <t>设备名称</t>
+  </si>
+  <si>
+    <t>申请编号</t>
+  </si>
+  <si>
+    <t>代理商</t>
   </si>
 </sst>
 </file>
@@ -596,117 +614,139 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" customWidth="1"/>
-    <col min="11" max="11" width="32.42578125" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" customWidth="1"/>
-    <col min="13" max="13" width="23.85546875" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" customWidth="1"/>
-    <col min="15" max="15" width="16.85546875" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" customWidth="1"/>
-    <col min="17" max="18" width="16.7109375" customWidth="1"/>
-    <col min="19" max="19" width="19.42578125" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" customWidth="1"/>
-    <col min="22" max="22" width="23.28515625" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
-    <col min="24" max="24" width="13.85546875" customWidth="1"/>
-    <col min="25" max="25" width="17.5703125" customWidth="1"/>
-    <col min="26" max="26" width="18.140625" customWidth="1"/>
-    <col min="27" max="27" width="20" customWidth="1"/>
-    <col min="28" max="28" width="29.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.28515625" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" customWidth="1"/>
+    <col min="17" max="17" width="32.42578125" customWidth="1"/>
+    <col min="18" max="18" width="19.7109375" customWidth="1"/>
+    <col min="19" max="19" width="23.85546875" customWidth="1"/>
+    <col min="20" max="20" width="13.28515625" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" customWidth="1"/>
+    <col min="23" max="24" width="16.7109375" customWidth="1"/>
+    <col min="25" max="25" width="19.42578125" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" customWidth="1"/>
+    <col min="28" max="28" width="23.28515625" customWidth="1"/>
+    <col min="29" max="29" width="14" customWidth="1"/>
+    <col min="30" max="30" width="13.85546875" customWidth="1"/>
+    <col min="31" max="31" width="17.5703125" customWidth="1"/>
+    <col min="32" max="32" width="18.140625" customWidth="1"/>
+    <col min="33" max="33" width="20" customWidth="1"/>
+    <col min="34" max="34" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:34" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -718,38 +758,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="42.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="42.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -761,7 +805,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -778,44 +822,47 @@
     <col min="13" max="13" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>46</v>
       </c>
     </row>
@@ -827,10 +874,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AAC19D1-83E1-40A1-A742-B0FE561C9C0F}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" customWidth="1"/>
@@ -840,29 +887,32 @@
     <col min="8" max="8" width="42.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>1</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FE766B-09F4-4813-9926-9F604D654B89}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0689D396-ED94-4F96-AF03-E844B09E210A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -134,9 +134,6 @@
     <t>订单紧急的原因</t>
   </si>
   <si>
-    <t>订单数量</t>
-  </si>
-  <si>
     <t>收货人</t>
   </si>
   <si>
@@ -216,6 +213,9 @@
   </si>
   <si>
     <t>代理商</t>
+  </si>
+  <si>
+    <t>订单数量/订单名额</t>
   </si>
 </sst>
 </file>
@@ -630,7 +630,7 @@
     <col min="17" max="17" width="32.42578125" customWidth="1"/>
     <col min="18" max="18" width="19.7109375" customWidth="1"/>
     <col min="19" max="19" width="23.85546875" customWidth="1"/>
-    <col min="20" max="20" width="13.28515625" customWidth="1"/>
+    <col min="20" max="20" width="27.140625" customWidth="1"/>
     <col min="21" max="21" width="16.85546875" customWidth="1"/>
     <col min="22" max="22" width="14.7109375" customWidth="1"/>
     <col min="23" max="24" width="16.7109375" customWidth="1"/>
@@ -648,22 +648,22 @@
   <sheetData>
     <row r="1" spans="1:34" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>15</v>
@@ -705,28 +705,28 @@
         <v>25</v>
       </c>
       <c r="T1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="U1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="AB1" s="3" t="s">
         <v>11</v>
@@ -738,13 +738,13 @@
         <v>14</v>
       </c>
       <c r="AE1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="AG1" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="AH1" s="3" t="s">
         <v>1</v>
@@ -773,10 +773,10 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -824,25 +824,25 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>10</v>
@@ -851,19 +851,19 @@
         <v>11</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -889,19 +889,19 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -910,7 +910,7 @@
         <v>11</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>

--- a/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0689D396-ED94-4F96-AF03-E844B09E210A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83E6885-3058-4E0F-B02B-3757E5880BE0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
-    <sheet name="额度信息" sheetId="1" r:id="rId1"/>
-    <sheet name="额度明细" sheetId="2" r:id="rId2"/>
+    <sheet name="维修工单" sheetId="1" r:id="rId1"/>
+    <sheet name="备件明细" sheetId="2" r:id="rId2"/>
     <sheet name="探头明细" sheetId="3" r:id="rId3"/>
-    <sheet name="归还信息" sheetId="4" r:id="rId4"/>
+    <sheet name="归还明细" sheetId="4" r:id="rId4"/>
+    <sheet name="维修工单报表" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="54">
   <si>
     <t>区域</t>
   </si>
@@ -805,7 +806,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -813,16 +814,17 @@
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
     <col min="4" max="4" width="25.85546875" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" customWidth="1"/>
-    <col min="8" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" customWidth="1"/>
+    <col min="9" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" customWidth="1"/>
+    <col min="14" max="14" width="19.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>51</v>
       </c>
@@ -841,28 +843,31 @@
       <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>45</v>
       </c>
     </row>
@@ -920,4 +925,170 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644DDB6A-FFA4-49B3-B3EB-E6F6582E54C5}">
+  <dimension ref="A1:AT1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="27" max="28" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.7109375" customWidth="1"/>
+    <col min="35" max="35" width="19.140625" customWidth="1"/>
+    <col min="36" max="36" width="18.42578125" customWidth="1"/>
+    <col min="37" max="37" width="14.140625" customWidth="1"/>
+    <col min="38" max="38" width="22.85546875" customWidth="1"/>
+    <col min="39" max="39" width="13.140625" customWidth="1"/>
+    <col min="41" max="41" width="43" customWidth="1"/>
+    <col min="42" max="42" width="17.42578125" customWidth="1"/>
+    <col min="43" max="43" width="19.28515625" customWidth="1"/>
+    <col min="44" max="44" width="21.7109375" customWidth="1"/>
+    <col min="45" max="45" width="24.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:46" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.15">
+      <c r="A1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AR1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AS1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AT1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83E6885-3058-4E0F-B02B-3757E5880BE0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8ED185-2FA2-4F13-890C-7D2ECB0D631B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="维修工单" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="57">
   <si>
     <t>区域</t>
   </si>
@@ -217,6 +217,15 @@
   </si>
   <si>
     <t>订单数量/订单名额</t>
+  </si>
+  <si>
+    <t>技术支持审批备注</t>
+  </si>
+  <si>
+    <t>区域经理审批备注</t>
+  </si>
+  <si>
+    <t>销售总监审批备注</t>
   </si>
 </sst>
 </file>
@@ -615,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -645,9 +654,12 @@
     <col min="32" max="32" width="18.140625" customWidth="1"/>
     <col min="33" max="33" width="20" customWidth="1"/>
     <col min="34" max="34" width="29.140625" customWidth="1"/>
+    <col min="35" max="35" width="20.140625" customWidth="1"/>
+    <col min="36" max="36" width="22" customWidth="1"/>
+    <col min="37" max="37" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:37" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -749,6 +761,15 @@
       </c>
       <c r="AH1" s="3" t="s">
         <v>1</v>
+      </c>
+      <c r="AI1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8ED185-2FA2-4F13-890C-7D2ECB0D631B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD9DC87-D664-4EBB-983C-1A9E57AE44F5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="63">
   <si>
     <t>区域</t>
   </si>
@@ -226,6 +226,24 @@
   </si>
   <si>
     <t>销售总监审批备注</t>
+  </si>
+  <si>
+    <t>技术支持审批人</t>
+  </si>
+  <si>
+    <t>技术支持审批时间</t>
+  </si>
+  <si>
+    <t>区域经理审批时间</t>
+  </si>
+  <si>
+    <t>区域经理审批人</t>
+  </si>
+  <si>
+    <t>销售总监审批时间</t>
+  </si>
+  <si>
+    <t>销售总监审批人</t>
   </si>
 </sst>
 </file>
@@ -624,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AQ1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -654,12 +672,18 @@
     <col min="32" max="32" width="18.140625" customWidth="1"/>
     <col min="33" max="33" width="20" customWidth="1"/>
     <col min="34" max="34" width="29.140625" customWidth="1"/>
-    <col min="35" max="35" width="20.140625" customWidth="1"/>
-    <col min="36" max="36" width="22" customWidth="1"/>
-    <col min="37" max="37" width="23.28515625" customWidth="1"/>
+    <col min="35" max="35" width="21.85546875" customWidth="1"/>
+    <col min="36" max="36" width="22.5703125" customWidth="1"/>
+    <col min="37" max="37" width="20.140625" customWidth="1"/>
+    <col min="38" max="38" width="21.85546875" customWidth="1"/>
+    <col min="39" max="39" width="22.5703125" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="21.85546875" customWidth="1"/>
+    <col min="42" max="42" width="22.5703125" customWidth="1"/>
+    <col min="43" max="43" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:43" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -763,12 +787,30 @@
         <v>1</v>
       </c>
       <c r="AI1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AN1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AP1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
         <v>56</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD9DC87-D664-4EBB-983C-1A9E57AE44F5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09422F32-063F-468B-A0CA-261C8FA01A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="358" activeTab="4" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="维修工单" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="65">
   <si>
     <t>区域</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>销售总监审批人</t>
+  </si>
+  <si>
+    <t>是否需要SSA Key</t>
+  </si>
+  <si>
+    <t>是否需要Dongle</t>
   </si>
 </sst>
 </file>
@@ -642,48 +648,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AQ1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AS1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.28515625" customWidth="1"/>
-    <col min="15" max="15" width="20.5703125" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" customWidth="1"/>
-    <col min="17" max="17" width="32.42578125" customWidth="1"/>
-    <col min="18" max="18" width="19.7109375" customWidth="1"/>
-    <col min="19" max="19" width="23.85546875" customWidth="1"/>
-    <col min="20" max="20" width="27.140625" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" customWidth="1"/>
-    <col min="23" max="24" width="16.7109375" customWidth="1"/>
-    <col min="25" max="25" width="19.42578125" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" customWidth="1"/>
-    <col min="28" max="28" width="23.28515625" customWidth="1"/>
-    <col min="29" max="29" width="14" customWidth="1"/>
-    <col min="30" max="30" width="13.85546875" customWidth="1"/>
-    <col min="31" max="31" width="17.5703125" customWidth="1"/>
-    <col min="32" max="32" width="18.140625" customWidth="1"/>
-    <col min="33" max="33" width="20" customWidth="1"/>
-    <col min="34" max="34" width="29.140625" customWidth="1"/>
-    <col min="35" max="35" width="21.85546875" customWidth="1"/>
-    <col min="36" max="36" width="22.5703125" customWidth="1"/>
-    <col min="37" max="37" width="20.140625" customWidth="1"/>
-    <col min="38" max="38" width="21.85546875" customWidth="1"/>
-    <col min="39" max="39" width="22.5703125" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="21.85546875" customWidth="1"/>
-    <col min="42" max="42" width="22.5703125" customWidth="1"/>
-    <col min="43" max="43" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" customWidth="1"/>
+    <col min="12" max="13" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.33203125" customWidth="1"/>
+    <col min="15" max="15" width="20.5546875" customWidth="1"/>
+    <col min="16" max="16" width="14.88671875" customWidth="1"/>
+    <col min="17" max="17" width="32.44140625" customWidth="1"/>
+    <col min="18" max="18" width="19.6640625" customWidth="1"/>
+    <col min="19" max="19" width="23.88671875" customWidth="1"/>
+    <col min="20" max="22" width="27.109375" customWidth="1"/>
+    <col min="23" max="23" width="16.88671875" customWidth="1"/>
+    <col min="24" max="24" width="14.6640625" customWidth="1"/>
+    <col min="25" max="26" width="16.6640625" customWidth="1"/>
+    <col min="27" max="27" width="19.44140625" customWidth="1"/>
+    <col min="28" max="28" width="14.6640625" customWidth="1"/>
+    <col min="29" max="29" width="14.33203125" customWidth="1"/>
+    <col min="30" max="30" width="23.33203125" customWidth="1"/>
+    <col min="31" max="31" width="14" customWidth="1"/>
+    <col min="32" max="32" width="13.88671875" customWidth="1"/>
+    <col min="33" max="33" width="17.5546875" customWidth="1"/>
+    <col min="34" max="34" width="18.109375" customWidth="1"/>
+    <col min="35" max="35" width="20" customWidth="1"/>
+    <col min="36" max="36" width="29.109375" customWidth="1"/>
+    <col min="37" max="37" width="21.88671875" customWidth="1"/>
+    <col min="38" max="38" width="22.5546875" customWidth="1"/>
+    <col min="39" max="39" width="20.109375" customWidth="1"/>
+    <col min="40" max="40" width="21.88671875" customWidth="1"/>
+    <col min="41" max="41" width="22.5546875" customWidth="1"/>
+    <col min="42" max="42" width="22" customWidth="1"/>
+    <col min="43" max="43" width="21.88671875" customWidth="1"/>
+    <col min="44" max="44" width="22.5546875" customWidth="1"/>
+    <col min="45" max="45" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:45" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -745,72 +751,78 @@
         <v>53</v>
       </c>
       <c r="U1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>56</v>
       </c>
     </row>
@@ -823,19 +835,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="42.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="8" width="42.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>51</v>
       </c>
@@ -870,24 +882,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" customWidth="1"/>
-    <col min="9" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
-    <col min="12" max="12" width="18.85546875" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" customWidth="1"/>
-    <col min="14" max="14" width="19.7109375" customWidth="1"/>
-    <col min="15" max="15" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="7" width="14.44140625" customWidth="1"/>
+    <col min="8" max="8" width="22.88671875" customWidth="1"/>
+    <col min="9" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" customWidth="1"/>
+    <col min="12" max="12" width="18.88671875" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" customWidth="1"/>
+    <col min="14" max="14" width="19.6640625" customWidth="1"/>
+    <col min="15" max="15" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>51</v>
       </c>
@@ -943,19 +955,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AAC19D1-83E1-40A1-A742-B0FE561C9C0F}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="28.140625" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="42.85546875" customWidth="1"/>
+    <col min="8" max="8" width="42.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>51</v>
       </c>
@@ -992,25 +1004,26 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644DDB6A-FFA4-49B3-B3EB-E6F6582E54C5}">
-  <dimension ref="A1:AT1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AV1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="27" max="28" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.7109375" customWidth="1"/>
-    <col min="35" max="35" width="19.140625" customWidth="1"/>
-    <col min="36" max="36" width="18.42578125" customWidth="1"/>
-    <col min="37" max="37" width="14.140625" customWidth="1"/>
-    <col min="38" max="38" width="22.85546875" customWidth="1"/>
-    <col min="39" max="39" width="13.140625" customWidth="1"/>
-    <col min="41" max="41" width="43" customWidth="1"/>
-    <col min="42" max="42" width="17.42578125" customWidth="1"/>
-    <col min="43" max="43" width="19.28515625" customWidth="1"/>
-    <col min="44" max="44" width="21.7109375" customWidth="1"/>
-    <col min="45" max="45" width="24.85546875" customWidth="1"/>
+    <col min="21" max="22" width="28.6640625" customWidth="1"/>
+    <col min="29" max="30" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.6640625" customWidth="1"/>
+    <col min="37" max="37" width="19.109375" customWidth="1"/>
+    <col min="38" max="38" width="18.44140625" customWidth="1"/>
+    <col min="39" max="39" width="14.109375" customWidth="1"/>
+    <col min="40" max="40" width="22.88671875" customWidth="1"/>
+    <col min="41" max="41" width="13.109375" customWidth="1"/>
+    <col min="43" max="43" width="43" customWidth="1"/>
+    <col min="44" max="44" width="17.44140625" customWidth="1"/>
+    <col min="45" max="45" width="19.33203125" customWidth="1"/>
+    <col min="46" max="46" width="21.6640625" customWidth="1"/>
+    <col min="47" max="47" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:48" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -1072,81 +1085,87 @@
         <v>53</v>
       </c>
       <c r="U1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>9</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09422F32-063F-468B-A0CA-261C8FA01A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF6F03C-8523-471A-AA61-2CF74F31BF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="358" activeTab="4" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="维修工单" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="66">
   <si>
     <t>区域</t>
   </si>
@@ -66,6 +66,8 @@
         <sz val="13.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>SN(序列号)</t>
     </r>
@@ -79,6 +81,8 @@
         <sz val="13.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>注（说明是否DOA或者Short life）</t>
     </r>
@@ -250,17 +254,21 @@
   </si>
   <si>
     <t>是否需要Dongle</t>
+  </si>
+  <si>
+    <t>下单时间</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -268,21 +276,36 @@
       <sz val="12"/>
       <color rgb="FF172B4D"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13.5"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -336,7 +359,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -352,7 +375,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -648,48 +671,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AS1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AT1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" customWidth="1"/>
-    <col min="12" max="13" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.33203125" customWidth="1"/>
-    <col min="15" max="15" width="20.5546875" customWidth="1"/>
-    <col min="16" max="16" width="14.88671875" customWidth="1"/>
-    <col min="17" max="17" width="32.44140625" customWidth="1"/>
-    <col min="18" max="18" width="19.6640625" customWidth="1"/>
-    <col min="19" max="19" width="23.88671875" customWidth="1"/>
-    <col min="20" max="22" width="27.109375" customWidth="1"/>
-    <col min="23" max="23" width="16.88671875" customWidth="1"/>
-    <col min="24" max="24" width="14.6640625" customWidth="1"/>
-    <col min="25" max="26" width="16.6640625" customWidth="1"/>
-    <col min="27" max="27" width="19.44140625" customWidth="1"/>
-    <col min="28" max="28" width="14.6640625" customWidth="1"/>
-    <col min="29" max="29" width="14.33203125" customWidth="1"/>
-    <col min="30" max="30" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="16.125" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="13" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.375" customWidth="1"/>
+    <col min="15" max="15" width="20.5" customWidth="1"/>
+    <col min="16" max="16" width="14.875" customWidth="1"/>
+    <col min="17" max="17" width="32.5" customWidth="1"/>
+    <col min="18" max="18" width="19.625" customWidth="1"/>
+    <col min="19" max="19" width="23.875" customWidth="1"/>
+    <col min="20" max="22" width="27.125" customWidth="1"/>
+    <col min="23" max="23" width="16.875" customWidth="1"/>
+    <col min="24" max="24" width="14.625" customWidth="1"/>
+    <col min="25" max="26" width="16.625" customWidth="1"/>
+    <col min="27" max="27" width="19.5" customWidth="1"/>
+    <col min="28" max="28" width="14.625" customWidth="1"/>
+    <col min="29" max="29" width="14.375" customWidth="1"/>
+    <col min="30" max="30" width="23.375" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="13.88671875" customWidth="1"/>
-    <col min="33" max="33" width="17.5546875" customWidth="1"/>
-    <col min="34" max="34" width="18.109375" customWidth="1"/>
+    <col min="32" max="32" width="13.875" customWidth="1"/>
+    <col min="33" max="33" width="17.5" customWidth="1"/>
+    <col min="34" max="34" width="18.125" customWidth="1"/>
     <col min="35" max="35" width="20" customWidth="1"/>
-    <col min="36" max="36" width="29.109375" customWidth="1"/>
-    <col min="37" max="37" width="21.88671875" customWidth="1"/>
-    <col min="38" max="38" width="22.5546875" customWidth="1"/>
-    <col min="39" max="39" width="20.109375" customWidth="1"/>
-    <col min="40" max="40" width="21.88671875" customWidth="1"/>
-    <col min="41" max="41" width="22.5546875" customWidth="1"/>
+    <col min="36" max="36" width="29.125" customWidth="1"/>
+    <col min="37" max="37" width="21.875" customWidth="1"/>
+    <col min="38" max="38" width="22.5" customWidth="1"/>
+    <col min="39" max="39" width="20.125" customWidth="1"/>
+    <col min="40" max="40" width="21.875" customWidth="1"/>
+    <col min="41" max="41" width="22.5" customWidth="1"/>
     <col min="42" max="42" width="22" customWidth="1"/>
-    <col min="43" max="43" width="21.88671875" customWidth="1"/>
-    <col min="44" max="44" width="22.5546875" customWidth="1"/>
-    <col min="45" max="45" width="23.33203125" customWidth="1"/>
+    <col min="43" max="43" width="21.875" customWidth="1"/>
+    <col min="44" max="45" width="22.5" customWidth="1"/>
+    <col min="46" max="46" width="23.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" s="6" customFormat="1">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -823,10 +846,14 @@
         <v>61</v>
       </c>
       <c r="AS1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT1" s="3" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -835,19 +862,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="8" width="42.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="4" max="4" width="15.5" customWidth="1"/>
+    <col min="5" max="5" width="20.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="42.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18">
       <c r="A1" s="3" t="s">
         <v>51</v>
       </c>
@@ -874,6 +901,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -882,24 +910,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="25.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="7" width="14.44140625" customWidth="1"/>
-    <col min="8" max="8" width="22.88671875" customWidth="1"/>
-    <col min="9" max="10" width="17.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.5546875" customWidth="1"/>
-    <col min="12" max="12" width="18.88671875" customWidth="1"/>
-    <col min="13" max="13" width="19.44140625" customWidth="1"/>
-    <col min="14" max="14" width="19.6640625" customWidth="1"/>
-    <col min="15" max="15" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="17.625" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="22.875" customWidth="1"/>
+    <col min="9" max="10" width="17.625" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="18.875" customWidth="1"/>
+    <col min="13" max="13" width="19.5" customWidth="1"/>
+    <col min="14" max="14" width="19.625" customWidth="1"/>
+    <col min="15" max="15" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>51</v>
       </c>
@@ -947,6 +975,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -955,19 +984,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AAC19D1-83E1-40A1-A742-B0FE561C9C0F}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="28.125" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="42.88671875" customWidth="1"/>
+    <col min="8" max="8" width="42.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>51</v>
       </c>
@@ -997,6 +1026,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1005,25 +1035,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644DDB6A-FFA4-49B3-B3EB-E6F6582E54C5}">
   <dimension ref="A1:AV1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="21" max="22" width="28.6640625" customWidth="1"/>
-    <col min="29" max="30" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.6640625" customWidth="1"/>
-    <col min="37" max="37" width="19.109375" customWidth="1"/>
-    <col min="38" max="38" width="18.44140625" customWidth="1"/>
-    <col min="39" max="39" width="14.109375" customWidth="1"/>
-    <col min="40" max="40" width="22.88671875" customWidth="1"/>
-    <col min="41" max="41" width="13.109375" customWidth="1"/>
+    <col min="21" max="22" width="28.625" customWidth="1"/>
+    <col min="29" max="30" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.625" customWidth="1"/>
+    <col min="37" max="37" width="19.125" customWidth="1"/>
+    <col min="38" max="38" width="18.5" customWidth="1"/>
+    <col min="39" max="39" width="14.125" customWidth="1"/>
+    <col min="40" max="40" width="22.875" customWidth="1"/>
+    <col min="41" max="41" width="13.125" customWidth="1"/>
     <col min="43" max="43" width="43" customWidth="1"/>
-    <col min="44" max="44" width="17.44140625" customWidth="1"/>
-    <col min="45" max="45" width="19.33203125" customWidth="1"/>
-    <col min="46" max="46" width="21.6640625" customWidth="1"/>
-    <col min="47" max="47" width="24.88671875" customWidth="1"/>
+    <col min="44" max="44" width="17.5" customWidth="1"/>
+    <col min="45" max="45" width="19.375" customWidth="1"/>
+    <col min="46" max="46" width="21.625" customWidth="1"/>
+    <col min="47" max="47" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" s="6" customFormat="1" ht="18">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -1170,6 +1200,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF6F03C-8523-471A-AA61-2CF74F31BF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2ABEF0-A4D8-4F75-AFA9-8D62ABE4DFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" activeTab="4" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="维修工单" sheetId="1" r:id="rId1"/>
@@ -679,6 +679,8 @@
     <col min="5" max="5" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="16.125" customWidth="1"/>
     <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="9" max="9" width="12.875" customWidth="1"/>
+    <col min="10" max="10" width="16.875" customWidth="1"/>
     <col min="11" max="11" width="14.125" customWidth="1"/>
     <col min="12" max="13" width="14.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.375" customWidth="1"/>
@@ -708,8 +710,9 @@
     <col min="41" max="41" width="22.5" customWidth="1"/>
     <col min="42" max="42" width="22" customWidth="1"/>
     <col min="43" max="43" width="21.875" customWidth="1"/>
-    <col min="44" max="45" width="22.5" customWidth="1"/>
-    <col min="46" max="46" width="23.375" customWidth="1"/>
+    <col min="44" max="44" width="22.5" customWidth="1"/>
+    <col min="45" max="45" width="23.375" customWidth="1"/>
+    <col min="46" max="46" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:46" s="6" customFormat="1">
@@ -846,10 +849,10 @@
         <v>61</v>
       </c>
       <c r="AS1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT1" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="AT1" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -988,7 +991,7 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20.375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="20.75" customWidth="1"/>
     <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="28.125" customWidth="1"/>
     <col min="6" max="6" width="16.5" customWidth="1"/>
@@ -1037,6 +1040,8 @@
   <dimension ref="A1:AV1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
+    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="10" max="10" width="19.5" customWidth="1"/>
     <col min="21" max="22" width="28.625" customWidth="1"/>
     <col min="29" max="30" width="10.125" bestFit="1" customWidth="1"/>
     <col min="33" max="34" width="14.875" bestFit="1" customWidth="1"/>

--- a/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/partOrder/excel/APM_ZKB_PartOrder_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\partOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2ABEF0-A4D8-4F75-AFA9-8D62ABE4DFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3025375E-05A9-4E42-915F-F2B125938D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" activeTab="4" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="29235" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="维修工单" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
   <si>
     <t>区域</t>
   </si>
@@ -259,6 +259,24 @@
     <t>下单时间</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>技术支持审批状态</t>
+  </si>
+  <si>
+    <t>区域经理审批状态</t>
+  </si>
+  <si>
+    <t>销售总监审批状态</t>
+  </si>
+  <si>
+    <t>下单状态</t>
+  </si>
+  <si>
+    <t>下单人</t>
+  </si>
+  <si>
+    <t>下单备注</t>
+  </si>
 </sst>
 </file>
 
@@ -268,7 +286,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -302,7 +320,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -359,7 +377,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -375,7 +393,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -671,51 +689,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AT1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:AZ1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.375" customWidth="1"/>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="9" max="9" width="12.875" customWidth="1"/>
-    <col min="10" max="10" width="16.875" customWidth="1"/>
-    <col min="11" max="11" width="14.125" customWidth="1"/>
-    <col min="12" max="13" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.375" customWidth="1"/>
-    <col min="15" max="15" width="20.5" customWidth="1"/>
-    <col min="16" max="16" width="14.875" customWidth="1"/>
-    <col min="17" max="17" width="32.5" customWidth="1"/>
-    <col min="18" max="18" width="19.625" customWidth="1"/>
-    <col min="19" max="19" width="23.875" customWidth="1"/>
-    <col min="20" max="22" width="27.125" customWidth="1"/>
-    <col min="23" max="23" width="16.875" customWidth="1"/>
-    <col min="24" max="24" width="14.625" customWidth="1"/>
-    <col min="25" max="26" width="16.625" customWidth="1"/>
-    <col min="27" max="27" width="19.5" customWidth="1"/>
-    <col min="28" max="28" width="14.625" customWidth="1"/>
-    <col min="29" max="29" width="14.375" customWidth="1"/>
-    <col min="30" max="30" width="23.375" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="20.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" customWidth="1"/>
+    <col min="17" max="17" width="32.42578125" customWidth="1"/>
+    <col min="18" max="18" width="19.5703125" customWidth="1"/>
+    <col min="19" max="19" width="23.85546875" customWidth="1"/>
+    <col min="20" max="22" width="27.140625" customWidth="1"/>
+    <col min="23" max="23" width="16.85546875" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" customWidth="1"/>
+    <col min="25" max="26" width="16.5703125" customWidth="1"/>
+    <col min="27" max="27" width="19.42578125" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" customWidth="1"/>
+    <col min="30" max="30" width="23.42578125" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="13.875" customWidth="1"/>
-    <col min="33" max="33" width="17.5" customWidth="1"/>
-    <col min="34" max="34" width="18.125" customWidth="1"/>
+    <col min="32" max="32" width="13.85546875" customWidth="1"/>
+    <col min="33" max="33" width="17.42578125" customWidth="1"/>
+    <col min="34" max="34" width="18.140625" customWidth="1"/>
     <col min="35" max="35" width="20" customWidth="1"/>
-    <col min="36" max="36" width="29.125" customWidth="1"/>
-    <col min="37" max="37" width="21.875" customWidth="1"/>
-    <col min="38" max="38" width="22.5" customWidth="1"/>
-    <col min="39" max="39" width="20.125" customWidth="1"/>
-    <col min="40" max="40" width="21.875" customWidth="1"/>
-    <col min="41" max="41" width="22.5" customWidth="1"/>
-    <col min="42" max="42" width="22" customWidth="1"/>
-    <col min="43" max="43" width="21.875" customWidth="1"/>
-    <col min="44" max="44" width="22.5" customWidth="1"/>
-    <col min="45" max="45" width="23.375" customWidth="1"/>
-    <col min="46" max="46" width="22.5" customWidth="1"/>
+    <col min="36" max="37" width="29.140625" customWidth="1"/>
+    <col min="38" max="38" width="21.85546875" customWidth="1"/>
+    <col min="39" max="39" width="22.42578125" customWidth="1"/>
+    <col min="40" max="41" width="20.140625" customWidth="1"/>
+    <col min="42" max="42" width="21.85546875" customWidth="1"/>
+    <col min="43" max="43" width="22.42578125" customWidth="1"/>
+    <col min="44" max="45" width="22" customWidth="1"/>
+    <col min="46" max="46" width="21.85546875" customWidth="1"/>
+    <col min="47" max="47" width="22.42578125" customWidth="1"/>
+    <col min="48" max="51" width="23.42578125" customWidth="1"/>
+    <col min="52" max="52" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="6" customFormat="1">
+    <row r="1" spans="1:52" s="6" customFormat="1" ht="14.25">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
@@ -825,33 +842,51 @@
         <v>1</v>
       </c>
       <c r="AK1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AT1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AX1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AY1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AZ1" s="3" t="s">
         <v>65</v>
       </c>
     </row>
@@ -865,16 +900,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.375" customWidth="1"/>
-    <col min="2" max="2" width="15.875" customWidth="1"/>
-    <col min="3" max="3" width="14.625" customWidth="1"/>
-    <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="20.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.875" customWidth="1"/>
-    <col min="8" max="8" width="42.625" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="42.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18">
@@ -913,21 +948,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="17.625" customWidth="1"/>
-    <col min="3" max="3" width="20.375" customWidth="1"/>
-    <col min="4" max="4" width="25.875" customWidth="1"/>
-    <col min="5" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="8" width="22.875" customWidth="1"/>
-    <col min="9" max="10" width="17.625" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="18.875" customWidth="1"/>
-    <col min="13" max="13" width="19.5" customWidth="1"/>
-    <col min="14" max="14" width="19.625" customWidth="1"/>
-    <col min="15" max="15" width="20.875" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" customWidth="1"/>
+    <col min="9" max="10" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" customWidth="1"/>
+    <col min="14" max="14" width="19.5703125" customWidth="1"/>
+    <col min="15" max="15" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -987,16 +1022,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AAC19D1-83E1-40A1-A742-B0FE561C9C0F}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="20.375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="20.75" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="28.125" customWidth="1"/>
-    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="42.875" customWidth="1"/>
+    <col min="8" max="8" width="42.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1038,24 +1073,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644DDB6A-FFA4-49B3-B3EB-E6F6582E54C5}">
   <dimension ref="A1:AV1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="9" max="9" width="14.375" customWidth="1"/>
-    <col min="10" max="10" width="19.5" customWidth="1"/>
-    <col min="21" max="22" width="28.625" customWidth="1"/>
-    <col min="29" max="30" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.625" customWidth="1"/>
-    <col min="37" max="37" width="19.125" customWidth="1"/>
-    <col min="38" max="38" width="18.5" customWidth="1"/>
-    <col min="39" max="39" width="14.125" customWidth="1"/>
-    <col min="40" max="40" width="22.875" customWidth="1"/>
-    <col min="41" max="41" width="13.125" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="21" max="22" width="28.5703125" customWidth="1"/>
+    <col min="29" max="30" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.5703125" customWidth="1"/>
+    <col min="37" max="37" width="19.140625" customWidth="1"/>
+    <col min="38" max="38" width="18.42578125" customWidth="1"/>
+    <col min="39" max="39" width="14.140625" customWidth="1"/>
+    <col min="40" max="40" width="22.85546875" customWidth="1"/>
+    <col min="41" max="41" width="13.140625" customWidth="1"/>
     <col min="43" max="43" width="43" customWidth="1"/>
-    <col min="44" max="44" width="17.5" customWidth="1"/>
-    <col min="45" max="45" width="19.375" customWidth="1"/>
-    <col min="46" max="46" width="21.625" customWidth="1"/>
-    <col min="47" max="47" width="24.875" customWidth="1"/>
+    <col min="44" max="44" width="17.42578125" customWidth="1"/>
+    <col min="45" max="45" width="19.42578125" customWidth="1"/>
+    <col min="46" max="46" width="21.5703125" customWidth="1"/>
+    <col min="47" max="47" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" s="6" customFormat="1" ht="18">
